--- a/GameData/DataTables/Business/MapTemplateConfig.xlsx
+++ b/GameData/DataTables/Business/MapTemplateConfig.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>#</t>
   </si>
   <si>
-    <t>Business table migrated from LegacyProjectArchive/Assets/Resources/DataTable/MapTemplateConfig.json. GF_X Id is numeric; original business keys are preserved as data columns.</t>
+    <t>六人纯 PVP 第一版只使用已完成的绿洲新城场景。</t>
   </si>
   <si>
     <t>Id</t>
@@ -59,40 +59,40 @@
     <t>float</t>
   </si>
   <si>
-    <t>GF_X numeric row id. Original business key is preserved as a data column when its name is not Id.</t>
+    <t>GF_X numeric row id.</t>
   </si>
   <si>
     <t>Note</t>
   </si>
   <si>
-    <t>主题枚举名（AI_RUINS / ALIEN_HIVE / VIRUS_SWAMP）</t>
-  </si>
-  <si>
-    <t>固定手工地图边界尺寸（单位 m，固定 400）</t>
-  </si>
-  <si>
-    <t>BSP 最小房间尺寸（单位 m）</t>
-  </si>
-  <si>
-    <t>BSP 最大递归深度（v2.1 = 4）</t>
-  </si>
-  <si>
-    <t>地块池 ID，用于 tile 替换。MVP 暂未消费</t>
-  </si>
-  <si>
-    <t>房间 Prefab 路径前缀（相对 Resources/Prefab/Map/）。MVP 留空</t>
-  </si>
-  <si>
-    <t>HUD 强调色（hex，如 #66CCFF）。透传字段</t>
-  </si>
-  <si>
-    <t>主色调（hex）。透传字段</t>
+    <t>场景主题名。</t>
+  </si>
+  <si>
+    <t>地图边界尺寸（米）。</t>
+  </si>
+  <si>
+    <t>运行时布局最小房间尺寸。</t>
+  </si>
+  <si>
+    <t>运行时布局最大递归深度。</t>
+  </si>
+  <si>
+    <t>地块池 ID。</t>
+  </si>
+  <si>
+    <t>场景或预制体路径。</t>
+  </si>
+  <si>
+    <t>HUD 强调色。</t>
+  </si>
+  <si>
+    <t>环境主色。</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>AI_RUINS</t>
+    <t>OASIS_CITY</t>
   </si>
   <si>
     <t>400.0</t>
@@ -107,40 +107,13 @@
     <t>101</t>
   </si>
   <si>
-    <t>#66CCFF</t>
-  </si>
-  <si>
-    <t>#3A4858</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>ALIEN_HIVE</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>#7DFF88</t>
-  </si>
-  <si>
-    <t>#273A22</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>VIRUS_SWAMP</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>#B6FF3C</t>
-  </si>
-  <si>
-    <t>#233A35</t>
+    <t>Assets/Game/Scene/OasisCity.unity</t>
+  </si>
+  <si>
+    <t>#379091</t>
+  </si>
+  <si>
+    <t>#B7824F</t>
   </si>
 </sst>
 </file>
@@ -328,85 +301,17 @@
         <v>30</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="J5" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="I6" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="J6" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="K6" s="0" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="I7" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="K7" s="0" t="s">
-        <v>42</v>
-      </c>
-    </row>
+    </row>
+    <row r="6"/>
+    <row r="7"/>
   </sheetData>
   <headerFooter/>
 </worksheet>
